--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_03_Chatbot vs ReAct Agent/Day_03_Phan_01_16_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_03_Chatbot vs ReAct Agent/Day_03_Phan_01_16_Cau.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -687,7 +687,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn mô tả trả lời được cả “tool làm gì” và “khi nào không nên dùng”.</t>
+          <t>Mô tả công cụ tốt phải nêu rõ công cụ làm gì và khi nào không nên dùng: 'Tra trạng thái đơn theo order_id; không dùng để đọc hồ sơ khách hàng' giúp mô hình phân biệt ranh giới chính xác nhất với customer_lookup.</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I10" s="4" t="n">
@@ -1007,7 +1007,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không chỉ kiểm kiểu mảng; còn phải kiểm schema của từng phần tử.</t>
+          <t>Trước khi thực thi lệnh gọi `book_room`, runtime cần: Kiểm tra tên tool có trong allowlist (a), Từ chối payload vì phần tử không đúng định dạng email (b), và Thêm Observation về lỗi kiểm tra chỉ rõ vị trí trường lỗi `attendees[0]` (c).</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,5</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
@@ -1329,7 +1329,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chỉ suy ra cạnh phụ thuộc từ các đầu vào đã được khai báo.</t>
+          <t>Phân tích đồ thị phụ thuộc (DAG): A (`get_user`), B (`get_weather`) và D (`log_request`) không phụ thuộc lẫn nhau nên có thể chạy song song (a); C (`recommend`) nhận đầu vào từ A và B nên bắt buộc phải chờ A và B hoàn tất (b); Chạy C quá sớm sẽ thiếu đầu vào (e).</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1432,7 +1432,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi luồng điều khiển khi cả hai điều kiện cùng đúng.</t>
+          <t>Lỗi luồng điều khiển là mã kiểm tra `if tool_call: execute(); append();` rồi rơi ngay xuống `if text: return text`, khiến phản hồi tạm 'Calling tool...' bị trả về như câu trả lời cuối cùng cho người dùng trước khi lượt gọi model kế tiếp có cơ hội đọc Observation.</t>
         </is>
       </c>
     </row>
